--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -9248,7 +9248,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20250928_100517.xlsx
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
